--- a/Base.xlsx
+++ b/Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fgvbr-my.sharepoint.com/personal/leonardo_cardoso_fgv_br/Documents/Área de Trabalho/Avaliação Itinerantes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_EDF4B5A5FD8F388FFFCDD8AA5CC643F97FE08429" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F635AC11-2F46-411C-9DD6-6EB124F2E9F4}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_EDF4B5A5FD8F388FFFCDD8AA5CC643F97FE08429" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A13E64E6-0F54-49AC-A3CD-C333177BAB24}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colaboradores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="262">
   <si>
     <t>AC</t>
   </si>
@@ -833,6 +833,12 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>sobrecarregado@fgv.br</t>
   </si>
 </sst>
 </file>
@@ -2984,7 +2990,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F849BD-A8DA-4D07-93B6-C60933B5F6AB}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
@@ -3057,6 +3063,15 @@
         <v>238</v>
       </c>
     </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{9731FEA5-4214-4056-ABC7-DDAE48807319}"/>
@@ -3064,6 +3079,7 @@
     <hyperlink ref="B3" r:id="rId3" xr:uid="{6A341163-4DD6-464C-8345-8F00AFC86B13}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{DF658387-9EF7-469D-91A6-10DCEF4F363C}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{54301C12-B595-4FAE-94B7-3B9364249F9F}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{728456B2-C395-432C-9B54-1C307545B853}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
